--- a/results/reliability_eval/Llama-3-8B_P17_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P17_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5701960930109592</v>
+        <v>0.5771953540866519</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6488847438225618</v>
+        <v>0.6572762810817295</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5701960930109592</v>
+        <v>0.5771953540866519</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6488847438225618</v>
+        <v>0.6572762810817295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4082159129870827</v>
+        <v>0.4146789299912405</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5484654316344773</v>
+        <v>0.5489498602024034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9952722045282738</v>
+        <v>0.9948706286638367</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9959974286441391</v>
+        <v>0.9961967028191627</v>
       </c>
       <c r="I2" t="n">
-        <v>0.589</v>
+        <v>0.612</v>
       </c>
     </row>
   </sheetData>
